--- a/tasks/finalpool/notion-team-survey-report/groundtruth_workspace/Survey_Analysis.xlsx
+++ b/tasks/finalpool/notion-team-survey-report/groundtruth_workspace/Survey_Analysis.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Responses" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Averages" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Highlights" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Survey Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary Statistics" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,32 +425,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
+          <t>Workload</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Workload</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Management_Support</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Comments</t>
+          <t>Growth</t>
         </is>
       </c>
     </row>
@@ -461,24 +450,18 @@
           <t>Alice</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Alpha</t>
-        </is>
+      <c r="B2" t="n">
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -486,24 +469,18 @@
           <t>Bob</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
+      <c r="B3" t="n">
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -511,24 +488,18 @@
           <t>Carol</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
+      <c r="B4" t="n">
+        <v>5</v>
       </c>
       <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -536,10 +507,8 @@
           <t>David</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
+      <c r="B5" t="n">
+        <v>3</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -548,12 +517,8 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -561,10 +526,8 @@
           <t>Eva</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Epsilon</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
@@ -575,10 +538,6 @@
       <c r="E6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -586,24 +545,18 @@
           <t>Frank</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Alpha</t>
-        </is>
+      <c r="B7" t="n">
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -611,24 +564,18 @@
           <t>Grace</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
       </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -636,74 +583,18 @@
           <t>Henry</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
       </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Irene</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Epsilon</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -716,305 +607,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Dimension</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Avg_Satisfaction</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Avg_Workload</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Avg_Collaboration</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Avg_Management_Support</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Overall_Score</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Response_Count</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="n">
         <v>3.5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Beta</t>
+          <t>Workload</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>3.5</v>
       </c>
-      <c r="C3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Delta</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
+        <v>3.625</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
         <v>3.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Best_Team</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Worst_Team</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Company_Average</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Satisfaction</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Alpha</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Workload</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Alpha</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Alpha</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Management_Support</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Gamma</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Overall_Score</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Epsilon</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>3.52</v>
       </c>
     </row>
   </sheetData>
